--- a/ConfigExcels/Npc.xlsx
+++ b/ConfigExcels/Npc.xlsx
@@ -143,7 +143,6 @@
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -194,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,9 +209,6 @@
     </xf>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -236,7 +232,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="baoxin li" id="{C5127693-6D81-F3A1-C655-48369624B224}" userId="baoxin li" providerId="Teamlab"/>
+  <person displayName="baoxin li" id="{12BAD18D-8633-FB82-F5BD-169D3D148735}" userId="baoxin li" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -720,13 +716,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-03-26T06:12:26.27Z" personId="{C5127693-6D81-F3A1-C655-48369624B224}" id="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}" done="0">
+  <threadedComment ref="C1" dT="2026-03-26T06:12:26.27Z" personId="{12BAD18D-8633-FB82-F5BD-169D3D148735}" id="{478F0CFA-DE5C-E7D5-58D5-DE934B6BD88B}" done="0">
     <text xml:space="preserve">1 = 消耗品
 2 = 材料
 3 = 任务物品
 </text>
   </threadedComment>
-  <threadedComment ref="F1" dT="2026-03-26T06:12:58.98Z" personId="{C5127693-6D81-F3A1-C655-48369624B224}" id="{7D911073-587C-38EB-81A1-AC28A1973EFA}" done="0">
+  <threadedComment ref="F1" dT="2026-03-26T06:12:58.98Z" personId="{12BAD18D-8633-FB82-F5BD-169D3D148735}" id="{7D911073-587C-38EB-81A1-AC28A1973EFA}" done="0">
     <text xml:space="preserve">1 = 普通
 2 = 优秀
 3 = 稀有
@@ -817,36 +813,36 @@
       <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>0</v>
       </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0</v>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>0</v>
       </c>
     </row>
